--- a/data/trans_dic/IP31KM02_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_2023-Provincia-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 24,41</t>
+          <t>3,27; 14,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 15,82</t>
+          <t>4,84; 16,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 16,0</t>
+          <t>5,06; 12,85</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,42; 53,13</t>
+          <t>36,89; 55,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,41; 55,59</t>
+          <t>38,44; 56,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,82; 50,73</t>
+          <t>39,96; 53,3</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,56%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,17; 53,87</t>
+          <t>36,79; 57,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,69; 55,89</t>
+          <t>32,41; 52,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,95; 52,1</t>
+          <t>37,24; 51,99</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>62,86%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,14; 77,55</t>
+          <t>35,46; 70,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,32; 70,17</t>
+          <t>59,36; 78,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,47; 70,34</t>
+          <t>49,79; 71,19</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>90,89; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,62; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95,6; 100,0</t>
+          <t>95,78; 100,0</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,86%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,56; 48,13</t>
+          <t>35,26; 57,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,63; 58,18</t>
+          <t>26,2; 48,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,89; 50,21</t>
+          <t>33,94; 49,82</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>58,72; 74,89</t>
+          <t>53,45; 69,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52,06; 70,48</t>
+          <t>59,58; 74,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57,14; 69,31</t>
+          <t>59,32; 70,03</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,16%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>73,76; 86,52</t>
+          <t>81,08; 91,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>82,21; 91,72</t>
+          <t>72,39; 86,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>80,21; 88,22</t>
+          <t>79,38; 88,05</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>59,67%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>48,81; 60,54</t>
+          <t>56,0; 63,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54,2; 61,97</t>
+          <t>56,07; 62,6</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53,5; 60,05</t>
+          <t>57,05; 62,33</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7970</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6093</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>9757</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3719; 17426</t>
+          <t>1968; 8476</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2549; 11802</t>
+          <t>2661; 9159</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7836; 23365</t>
+          <t>5827; 14803</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>49722</t>
+          <t>53290</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>58723</t>
+          <t>47230</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108445</t>
+          <t>100520</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21892; 66753</t>
+          <t>42405; 64345</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47297; 70280</t>
+          <t>38181; 55805</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>75176; 127877</t>
+          <t>85623; 114203</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1234,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23730</t>
+          <t>26701</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29661</t>
+          <t>22943</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53391</t>
+          <t>49644</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18425; 29926</t>
+          <t>21078; 32970</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23066; 36121</t>
+          <t>17539; 28608</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44408; 62614</t>
+          <t>41494; 57926</t>
         </is>
       </c>
     </row>
@@ -1307,12 +1307,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>47552</t>
+          <t>39543</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42171</t>
+          <t>48638</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89723</t>
+          <t>88181</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39814; 54041</t>
+          <t>24757; 49435</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25112; 52883</t>
+          <t>41827; 55204</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65951; 102032</t>
+          <t>69851; 99857</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>39579</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74052</t>
+          <t>74145</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31085; 34200</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>32054; 35370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71625; 74919</t>
+          <t>71784; 74949</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>16394</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41587</t>
+          <t>38303</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11763; 21316</t>
+          <t>16646; 27186</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19165; 31289</t>
+          <t>11604; 21382</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>34221; 49245</t>
+          <t>31052; 45585</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>119</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>83172</t>
+          <t>87734</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>96332</t>
+          <t>82059</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>179505</t>
+          <t>169793</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>72632; 92633</t>
+          <t>75139; 98155</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>80714; 109278</t>
+          <t>72584; 90297</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>159262; 193195</t>
+          <t>155649; 183743</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>154</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>104447</t>
+          <t>137550</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>134728</t>
+          <t>110761</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>239175</t>
+          <t>248311</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>94909; 111323</t>
+          <t>127405; 144412</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>126740; 141401</t>
+          <t>99821; 119383</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>226859; 249518</t>
+          <t>234193; 259777</t>
         </is>
       </c>
     </row>
@@ -1672,12 +1672,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>544</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>366321</t>
+          <t>410834</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>433620</t>
+          <t>367819</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>799941</t>
+          <t>778653</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>318794; 395379</t>
+          <t>384652; 434676</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>403613; 461505</t>
+          <t>346615; 386977</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>747858; 839350</t>
+          <t>744514; 813442</t>
         </is>
       </c>
     </row>
